--- a/artfynd/A 33577-2021 artfynd.xlsx
+++ b/artfynd/A 33577-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33577-2021 artfynd.xlsx
+++ b/artfynd/A 33577-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94778629</v>
+        <v>94778591</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555642.7820697654</v>
+        <v>555563</v>
       </c>
       <c r="R2" t="n">
-        <v>7099350.839224639</v>
+        <v>7099389</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,19 +746,9 @@
           <t>2021-07-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-07-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,43 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94778644</v>
+        <v>94778629</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555694.655212577</v>
+        <v>555643</v>
       </c>
       <c r="R3" t="n">
-        <v>7099274.563609326</v>
+        <v>7099350</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -868,19 +847,9 @@
           <t>2021-07-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-07-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,42 +877,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94778591</v>
+        <v>94778644</v>
       </c>
       <c r="B4" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555563.4840990361</v>
+        <v>555695</v>
       </c>
       <c r="R4" t="n">
-        <v>7099388.901663737</v>
+        <v>7099274</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,19 +949,9 @@
           <t>2021-07-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-07-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
